--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -68,7 +68,7 @@
     <t>5001,5011</t>
   </si>
   <si>
-    <t>100,100</t>
+    <t>100,10</t>
   </si>
   <si>
     <t>2,1</t>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="21">
   <si>
     <t>_Id</t>
   </si>
@@ -84,6 +84,12 @@
   </si>
   <si>
     <t>5001,5014</t>
+  </si>
+  <si>
+    <t>200,100</t>
+  </si>
+  <si>
+    <t>100,1</t>
   </si>
 </sst>
 </file>
@@ -1160,7 +1166,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>12</v>
@@ -1189,7 +1195,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
@@ -1218,7 +1224,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>17</v>
@@ -1247,7 +1253,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>18</v>
@@ -1273,22 +1279,22 @@
         <v>1001</v>
       </c>
       <c r="F10" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G10" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>12</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="3:12">
@@ -1302,22 +1308,22 @@
         <v>1002</v>
       </c>
       <c r="F11" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G11" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>16</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J11" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="3:12">
@@ -1331,22 +1337,22 @@
         <v>1003</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G12" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J12" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="3:12">
@@ -1360,22 +1366,22 @@
         <v>1004</v>
       </c>
       <c r="F13" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G13" s="1">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>18</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="J13" s="3" t="s">
         <v>14</v>
       </c>
       <c r="K13" s="3" t="s">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
   <si>
     <t>_Id</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>100,1</t>
+  </si>
+  <si>
+    <t>300,1000</t>
+  </si>
+  <si>
+    <t>1000,1</t>
   </si>
 </sst>
 </file>
@@ -1048,7 +1054,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L13"/>
+  <dimension ref="C3:L17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1384,6 +1390,122 @@
         <v>20</v>
       </c>
     </row>
+    <row r="14" customHeight="1" spans="3:12">
+      <c r="C14" s="1">
+        <v>9</v>
+      </c>
+      <c r="D14" s="1">
+        <v>6</v>
+      </c>
+      <c r="E14" s="1">
+        <v>1001</v>
+      </c>
+      <c r="F14" s="1">
+        <v>11</v>
+      </c>
+      <c r="G14" s="1">
+        <v>15</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:12">
+      <c r="C15" s="1">
+        <v>10</v>
+      </c>
+      <c r="D15" s="1">
+        <v>6</v>
+      </c>
+      <c r="E15" s="1">
+        <v>1002</v>
+      </c>
+      <c r="F15" s="1">
+        <v>11</v>
+      </c>
+      <c r="G15" s="1">
+        <v>15</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K15" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:12">
+      <c r="C16" s="1">
+        <v>11</v>
+      </c>
+      <c r="D16" s="1">
+        <v>6</v>
+      </c>
+      <c r="E16" s="1">
+        <v>1003</v>
+      </c>
+      <c r="F16" s="1">
+        <v>11</v>
+      </c>
+      <c r="G16" s="1">
+        <v>15</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:11">
+      <c r="C17" s="1">
+        <v>12</v>
+      </c>
+      <c r="D17" s="1">
+        <v>6</v>
+      </c>
+      <c r="E17" s="1">
+        <v>1004</v>
+      </c>
+      <c r="F17" s="1">
+        <v>11</v>
+      </c>
+      <c r="G17" s="1">
+        <v>15</v>
+      </c>
+      <c r="H17" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
   </sheetData>
   <dataValidations count="1">
     <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:D5" errorStyle="warning">

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="25">
   <si>
     <t>_Id</t>
   </si>
@@ -71,22 +71,28 @@
     <t>100,10</t>
   </si>
   <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>10,1</t>
+  </si>
+  <si>
+    <t>5001,5012</t>
+  </si>
+  <si>
+    <t>5001,5013</t>
+  </si>
+  <si>
+    <t>5001,5014</t>
+  </si>
+  <si>
+    <t>#</t>
+  </si>
+  <si>
+    <t>200,100</t>
+  </si>
+  <si>
     <t>2,1</t>
-  </si>
-  <si>
-    <t>10,1</t>
-  </si>
-  <si>
-    <t>5001,5012</t>
-  </si>
-  <si>
-    <t>5001,5013</t>
-  </si>
-  <si>
-    <t>5001,5014</t>
-  </si>
-  <si>
-    <t>200,100</t>
   </si>
   <si>
     <t>100,1</t>
@@ -1054,7 +1060,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="C3:L17"/>
+  <dimension ref="A3:L17"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1068,7 +1074,7 @@
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="3:12">
+    <row r="3" customHeight="1" spans="1:12">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1098,7 +1104,7 @@
       </c>
       <c r="L3" s="2"/>
     </row>
-    <row r="4" customHeight="1" spans="3:12">
+    <row r="4" customHeight="1" spans="1:12">
       <c r="C4" s="2" t="s">
         <v>9</v>
       </c>
@@ -1128,7 +1134,7 @@
       </c>
       <c r="L4" s="2"/>
     </row>
-    <row r="5" customHeight="1" spans="3:12">
+    <row r="5" customHeight="1" spans="1:12">
       <c r="C5" s="2" t="s">
         <v>10</v>
       </c>
@@ -1158,7 +1164,7 @@
       </c>
       <c r="L5" s="2"/>
     </row>
-    <row r="6" customHeight="1" spans="3:12">
+    <row r="6" customHeight="1" spans="1:12">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1172,7 +1178,7 @@
         <v>1</v>
       </c>
       <c r="G6" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>12</v>
@@ -1187,7 +1193,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="7" customHeight="1" spans="3:12">
+    <row r="7" customHeight="1" spans="1:12">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1201,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="G7" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>16</v>
@@ -1216,7 +1222,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" customHeight="1" spans="3:12">
+    <row r="8" customHeight="1" spans="1:12">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1230,7 +1236,7 @@
         <v>1</v>
       </c>
       <c r="G8" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>17</v>
@@ -1245,7 +1251,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:12">
+    <row r="9" customHeight="1" spans="1:12">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1259,7 +1265,7 @@
         <v>1</v>
       </c>
       <c r="G9" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>18</v>
@@ -1274,7 +1280,13 @@
         <v>15</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:12">
+    <row r="10" customHeight="1" spans="1:12">
+      <c r="A10" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C10" s="1">
         <v>5</v>
       </c>
@@ -1294,16 +1306,22 @@
         <v>12</v>
       </c>
       <c r="I10" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="1:12">
+      <c r="A11" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:12">
+      <c r="B11" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C11" s="1">
         <v>6</v>
       </c>
@@ -1323,16 +1341,22 @@
         <v>16</v>
       </c>
       <c r="I11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="1:12">
+      <c r="A12" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:12">
+      <c r="B12" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C12" s="1">
         <v>7</v>
       </c>
@@ -1352,16 +1376,22 @@
         <v>17</v>
       </c>
       <c r="I12" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:12">
+      <c r="A13" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:12">
+      <c r="B13" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C13" s="1">
         <v>8</v>
       </c>
@@ -1381,16 +1411,22 @@
         <v>18</v>
       </c>
       <c r="I13" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="1:12">
+      <c r="A14" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:12">
+      <c r="B14" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C14" s="1">
         <v>9</v>
       </c>
@@ -1410,16 +1446,22 @@
         <v>12</v>
       </c>
       <c r="I14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J14" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J14" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="K14" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:12">
+    <row r="15" customHeight="1" spans="1:12">
+      <c r="A15" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C15" s="1">
         <v>10</v>
       </c>
@@ -1439,16 +1481,22 @@
         <v>16</v>
       </c>
       <c r="I15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J15" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J15" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="K15" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:12">
+    <row r="16" customHeight="1" spans="1:12">
+      <c r="A16" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C16" s="1">
         <v>11</v>
       </c>
@@ -1468,16 +1516,22 @@
         <v>17</v>
       </c>
       <c r="I16" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J16" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="K16" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
-    <row r="17" customHeight="1" spans="3:11">
+    <row r="17" customHeight="1" spans="1:11">
+      <c r="A17" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>19</v>
+      </c>
       <c r="C17" s="1">
         <v>12</v>
       </c>
@@ -1497,13 +1551,13 @@
         <v>18</v>
       </c>
       <c r="I17" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="J17" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="J17" s="3" t="s">
-        <v>14</v>
-      </c>
       <c r="K17" s="3" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>_Id</t>
   </si>
@@ -92,16 +92,7 @@
     <t>200,100</t>
   </si>
   <si>
-    <t>2,1</t>
-  </si>
-  <si>
     <t>100,1</t>
-  </si>
-  <si>
-    <t>300,1000</t>
-  </si>
-  <si>
-    <t>1000,1</t>
   </si>
 </sst>
 </file>
@@ -1060,7 +1051,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L17"/>
+  <dimension ref="A3:L13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1297,10 +1288,10 @@
         <v>1001</v>
       </c>
       <c r="F10" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G10" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>12</v>
@@ -1309,10 +1300,10 @@
         <v>20</v>
       </c>
       <c r="J10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K10" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="11" customHeight="1" spans="1:12">
@@ -1332,10 +1323,10 @@
         <v>1002</v>
       </c>
       <c r="F11" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G11" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>16</v>
@@ -1344,10 +1335,10 @@
         <v>20</v>
       </c>
       <c r="J11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K11" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="12" customHeight="1" spans="1:12">
@@ -1367,10 +1358,10 @@
         <v>1003</v>
       </c>
       <c r="F12" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G12" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>17</v>
@@ -1379,10 +1370,10 @@
         <v>20</v>
       </c>
       <c r="J12" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K12" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>22</v>
       </c>
     </row>
     <row r="13" customHeight="1" spans="1:12">
@@ -1402,10 +1393,10 @@
         <v>1004</v>
       </c>
       <c r="F13" s="1">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="G13" s="1">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>18</v>
@@ -1414,150 +1405,10 @@
         <v>20</v>
       </c>
       <c r="J13" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="K13" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="1:12">
-      <c r="A14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B14" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C14" s="1">
-        <v>9</v>
-      </c>
-      <c r="D14" s="1">
-        <v>6</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1001</v>
-      </c>
-      <c r="F14" s="1">
-        <v>11</v>
-      </c>
-      <c r="G14" s="1">
-        <v>15</v>
-      </c>
-      <c r="H14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="I14" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J14" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="1:12">
-      <c r="A15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C15" s="1">
-        <v>10</v>
-      </c>
-      <c r="D15" s="1">
-        <v>6</v>
-      </c>
-      <c r="E15" s="1">
-        <v>1002</v>
-      </c>
-      <c r="F15" s="1">
-        <v>11</v>
-      </c>
-      <c r="G15" s="1">
-        <v>15</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J15" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K15" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="1:12">
-      <c r="A16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C16" s="1">
-        <v>11</v>
-      </c>
-      <c r="D16" s="1">
-        <v>6</v>
-      </c>
-      <c r="E16" s="1">
-        <v>1003</v>
-      </c>
-      <c r="F16" s="1">
-        <v>11</v>
-      </c>
-      <c r="G16" s="1">
-        <v>15</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="I16" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="1:11">
-      <c r="A17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="C17" s="1">
-        <v>12</v>
-      </c>
-      <c r="D17" s="1">
-        <v>6</v>
-      </c>
-      <c r="E17" s="1">
-        <v>1004</v>
-      </c>
-      <c r="F17" s="1">
-        <v>11</v>
-      </c>
-      <c r="G17" s="1">
-        <v>15</v>
-      </c>
-      <c r="H17" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="I17" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>24</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/EquipGradeConfig.xlsx
+++ b/Excel/EquipGradeConfig.xlsx
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="19">
   <si>
     <t>_Id</t>
   </si>
@@ -53,9 +53,6 @@
     <t>RiseTypeList</t>
   </si>
   <si>
-    <t>RiseMcList</t>
-  </si>
-  <si>
     <t>Id</t>
   </si>
   <si>
@@ -68,13 +65,10 @@
     <t>5001,5011</t>
   </si>
   <si>
-    <t>100,10</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>10,1</t>
+    <t>1000,10</t>
+  </si>
+  <si>
+    <t>2,4</t>
   </si>
   <si>
     <t>5001,5012</t>
@@ -90,9 +84,6 @@
   </si>
   <si>
     <t>200,100</t>
-  </si>
-  <si>
-    <t>100,1</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1042,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A3:L13"/>
+  <dimension ref="A3:J13"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="18" customHeight="1"/>
   <cols>
     <col min="1" max="4" width="9" style="1"/>
@@ -1059,13 +1050,13 @@
     <col min="8" max="8" width="16.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="16" style="1" customWidth="1"/>
     <col min="10" max="10" width="10.5" style="1" customWidth="1"/>
-    <col min="11" max="11" width="16.125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="13.125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="12.25" style="1" customWidth="1"/>
+    <col min="11" max="11" width="12.25" style="1" customWidth="1"/>
+    <col min="12" max="12" width="9" style="1"/>
+    <col min="13" max="13" width="13.9166666666667" style="1" customWidth="1"/>
     <col min="14" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="3" customHeight="1" spans="1:12">
+    <row r="3" customHeight="1" spans="1:10">
       <c r="C3" s="2" t="s">
         <v>0</v>
       </c>
@@ -1090,14 +1081,10 @@
       <c r="J3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K3" s="2" t="s">
+    </row>
+    <row r="4" customHeight="1" spans="1:10">
+      <c r="C4" s="2" t="s">
         <v>8</v>
-      </c>
-      <c r="L3" s="2"/>
-    </row>
-    <row r="4" customHeight="1" spans="1:12">
-      <c r="C4" s="2" t="s">
-        <v>9</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>1</v>
@@ -1120,42 +1107,34 @@
       <c r="J4" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K4" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="L4" s="2"/>
     </row>
-    <row r="5" customHeight="1" spans="1:12">
+    <row r="5" customHeight="1" spans="1:10">
       <c r="C5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="H5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="I5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="J5" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="F5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="I5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="J5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="K5" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L5" s="2"/>
     </row>
-    <row r="6" customHeight="1" spans="1:12">
+    <row r="6" customHeight="1" spans="1:10">
       <c r="C6" s="1">
         <v>1</v>
       </c>
@@ -1172,19 +1151,16 @@
         <v>14</v>
       </c>
       <c r="H6" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="I6" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="J6" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="7" customHeight="1" spans="1:12">
+    <row r="7" customHeight="1" spans="1:10">
       <c r="C7" s="1">
         <v>2</v>
       </c>
@@ -1201,19 +1177,16 @@
         <v>14</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I7" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J7" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J7" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="8" customHeight="1" spans="1:12">
+    <row r="8" customHeight="1" spans="1:10">
       <c r="C8" s="1">
         <v>3</v>
       </c>
@@ -1230,19 +1203,16 @@
         <v>14</v>
       </c>
       <c r="H8" s="3" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="I8" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J8" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K8" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="9" customHeight="1" spans="1:12">
+    <row r="9" customHeight="1" spans="1:10">
       <c r="C9" s="1">
         <v>4</v>
       </c>
@@ -1259,24 +1229,21 @@
         <v>14</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="I9" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="J9" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="J9" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K9" s="3" t="s">
-        <v>15</v>
-      </c>
     </row>
-    <row r="10" customHeight="1" spans="1:12">
+    <row r="10" customHeight="1" spans="1:10">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C10" s="1">
         <v>5</v>
@@ -1294,24 +1261,21 @@
         <v>15</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="1:12">
+    <row r="11" customHeight="1" spans="1:10">
       <c r="A11" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1">
         <v>6</v>
@@ -1329,24 +1293,21 @@
         <v>15</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="1:12">
+    <row r="12" customHeight="1" spans="1:10">
       <c r="A12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C12" s="1">
         <v>7</v>
@@ -1364,24 +1325,21 @@
         <v>15</v>
       </c>
       <c r="H12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="I12" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="1:10">
+      <c r="A13" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="I12" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="1:12">
-      <c r="A13" s="1" t="s">
-        <v>19</v>
-      </c>
       <c r="B13" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C13" s="1">
         <v>8</v>
@@ -1399,16 +1357,13 @@
         <v>15</v>
       </c>
       <c r="H13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="I13" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="I13" s="3" t="s">
-        <v>20</v>
-      </c>
       <c r="J13" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>21</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>
